--- a/tools/kpi_tracker.xlsx
+++ b/tools/kpi_tracker.xlsx
@@ -107,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -133,6 +133,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -523,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -926,25 +929,103 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>YouTube Music 트래픽 비율</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>생성 확인 후 증가 추세</t>
+        </is>
+      </c>
+      <c r="D13" s="11">
+        <f>IF(ISNUMBER(E13),E13,"")</f>
+        <v/>
+      </c>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="9" t="n"/>
+      <c r="I13" s="9" t="n"/>
+      <c r="J13" s="7">
+        <f>IF(AND(ISNUMBER(E13),ISNUMBER(I13),E13&lt;&gt;0),I13/E13-1,"")</f>
+        <v/>
+      </c>
+      <c r="K13" s="4">
+        <f>IF(OR(NOT(ISNUMBER(I13)),D13=""),"",IF(I13&gt;=D13,"달성","미달"))</f>
+        <v/>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>트래픽 소스 중 YouTube Music 비율, 소수 입력. 유통 반영 전에는 빈칸</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>팟캐스트 트래픽 비율</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>생성 확인 후 증가 추세</t>
+        </is>
+      </c>
+      <c r="D14" s="11">
+        <f>IF(ISNUMBER(E14),E14,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="9" t="n"/>
+      <c r="I14" s="9" t="n"/>
+      <c r="J14" s="7">
+        <f>IF(AND(ISNUMBER(E14),ISNUMBER(I14),E14&lt;&gt;0),I14/E14-1,"")</f>
+        <v/>
+      </c>
+      <c r="K14" s="4">
+        <f>IF(OR(NOT(ISNUMBER(I14)),D14=""),"",IF(I14&gt;=D14,"달성","미달"))</f>
+        <v/>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>트래픽 소스 중 팟캐스트 비율, 소수 입력. RSS 연결 전에는 빈칸</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>달성 지표 수</t>
         </is>
       </c>
-      <c r="B14">
-        <f>COUNTIF(K5:K12,"달성")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="B16">
+        <f>COUNTIF(K5:K14,"달성")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>평가 가능 지표 수</t>
         </is>
       </c>
-      <c r="B15">
-        <f>COUNTIF(K5:K12,"달성")+COUNTIF(K5:K12,"미달")</f>
+      <c r="B17">
+        <f>COUNTIF(K5:K14,"달성")+COUNTIF(K5:K14,"미달")</f>
         <v/>
       </c>
     </row>
@@ -1034,452 +1115,452 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="n">
+      <c r="A2" s="13" t="n">
         <v>46287</v>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>아기 수면음악 | 잠 안 자는 신생아 5분 만에 재우는 자장가 10시간 광고없음</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>밤잠 10시간</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E2" s="13" t="n">
+      <c r="E2" s="14" t="n">
         <v>15000</v>
       </c>
-      <c r="F2" s="14" t="n">
+      <c r="F2" s="15" t="n">
         <v>0.045</v>
       </c>
-      <c r="G2" s="15" t="n">
+      <c r="G2" s="16" t="n">
         <v>14.2</v>
       </c>
-      <c r="H2" s="13" t="n">
+      <c r="H2" s="14" t="n">
         <v>42000</v>
       </c>
-      <c r="I2" s="13" t="n">
+      <c r="I2" s="14" t="n">
         <v>85</v>
       </c>
-      <c r="J2" s="13" t="n">
+      <c r="J2" s="14" t="n">
         <v>12</v>
       </c>
-      <c r="K2" s="13" t="inlineStr">
+      <c r="K2" s="14" t="inlineStr">
         <is>
           <t>예시 행. 실제 값으로 교체</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="n"/>
-      <c r="B3" s="13" t="n"/>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="13" t="n"/>
-      <c r="F3" s="14" t="n"/>
-      <c r="G3" s="15" t="n"/>
-      <c r="H3" s="13" t="n"/>
-      <c r="I3" s="13" t="n"/>
-      <c r="J3" s="13" t="n"/>
-      <c r="K3" s="13" t="n"/>
+      <c r="A3" s="13" t="n"/>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="15" t="n"/>
+      <c r="G3" s="16" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="14" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="n"/>
-      <c r="B4" s="13" t="n"/>
-      <c r="C4" s="13" t="n"/>
-      <c r="D4" s="13" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="14" t="n"/>
-      <c r="G4" s="15" t="n"/>
-      <c r="H4" s="13" t="n"/>
-      <c r="I4" s="13" t="n"/>
-      <c r="J4" s="13" t="n"/>
-      <c r="K4" s="13" t="n"/>
+      <c r="A4" s="13" t="n"/>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="16" t="n"/>
+      <c r="H4" s="14" t="n"/>
+      <c r="I4" s="14" t="n"/>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="14" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="n"/>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="14" t="n"/>
-      <c r="G5" s="15" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="n"/>
-      <c r="K5" s="13" t="n"/>
+      <c r="A5" s="13" t="n"/>
+      <c r="B5" s="14" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="15" t="n"/>
+      <c r="G5" s="16" t="n"/>
+      <c r="H5" s="14" t="n"/>
+      <c r="I5" s="14" t="n"/>
+      <c r="J5" s="14" t="n"/>
+      <c r="K5" s="14" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="n"/>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="15" t="n"/>
-      <c r="H6" s="13" t="n"/>
-      <c r="I6" s="13" t="n"/>
-      <c r="J6" s="13" t="n"/>
-      <c r="K6" s="13" t="n"/>
+      <c r="A6" s="13" t="n"/>
+      <c r="B6" s="14" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
+      <c r="E6" s="14" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+      <c r="H6" s="14" t="n"/>
+      <c r="I6" s="14" t="n"/>
+      <c r="J6" s="14" t="n"/>
+      <c r="K6" s="14" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="n"/>
-      <c r="B7" s="13" t="n"/>
-      <c r="C7" s="13" t="n"/>
-      <c r="D7" s="13" t="n"/>
-      <c r="E7" s="13" t="n"/>
-      <c r="F7" s="14" t="n"/>
-      <c r="G7" s="15" t="n"/>
-      <c r="H7" s="13" t="n"/>
-      <c r="I7" s="13" t="n"/>
-      <c r="J7" s="13" t="n"/>
-      <c r="K7" s="13" t="n"/>
+      <c r="A7" s="13" t="n"/>
+      <c r="B7" s="14" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="14" t="n"/>
+      <c r="E7" s="14" t="n"/>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="16" t="n"/>
+      <c r="H7" s="14" t="n"/>
+      <c r="I7" s="14" t="n"/>
+      <c r="J7" s="14" t="n"/>
+      <c r="K7" s="14" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="n"/>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="15" t="n"/>
-      <c r="H8" s="13" t="n"/>
-      <c r="I8" s="13" t="n"/>
-      <c r="J8" s="13" t="n"/>
-      <c r="K8" s="13" t="n"/>
+      <c r="A8" s="13" t="n"/>
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
+      <c r="E8" s="14" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="16" t="n"/>
+      <c r="H8" s="14" t="n"/>
+      <c r="I8" s="14" t="n"/>
+      <c r="J8" s="14" t="n"/>
+      <c r="K8" s="14" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="n"/>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="13" t="n"/>
-      <c r="D9" s="13" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="15" t="n"/>
-      <c r="H9" s="13" t="n"/>
-      <c r="I9" s="13" t="n"/>
-      <c r="J9" s="13" t="n"/>
-      <c r="K9" s="13" t="n"/>
+      <c r="A9" s="13" t="n"/>
+      <c r="B9" s="14" t="n"/>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="14" t="n"/>
+      <c r="E9" s="14" t="n"/>
+      <c r="F9" s="15" t="n"/>
+      <c r="G9" s="16" t="n"/>
+      <c r="H9" s="14" t="n"/>
+      <c r="I9" s="14" t="n"/>
+      <c r="J9" s="14" t="n"/>
+      <c r="K9" s="14" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="n"/>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="15" t="n"/>
-      <c r="H10" s="13" t="n"/>
-      <c r="I10" s="13" t="n"/>
-      <c r="J10" s="13" t="n"/>
-      <c r="K10" s="13" t="n"/>
+      <c r="A10" s="13" t="n"/>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="16" t="n"/>
+      <c r="H10" s="14" t="n"/>
+      <c r="I10" s="14" t="n"/>
+      <c r="J10" s="14" t="n"/>
+      <c r="K10" s="14" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="n"/>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="13" t="n"/>
-      <c r="E11" s="13" t="n"/>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="15" t="n"/>
-      <c r="H11" s="13" t="n"/>
-      <c r="I11" s="13" t="n"/>
-      <c r="J11" s="13" t="n"/>
-      <c r="K11" s="13" t="n"/>
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="16" t="n"/>
+      <c r="H11" s="14" t="n"/>
+      <c r="I11" s="14" t="n"/>
+      <c r="J11" s="14" t="n"/>
+      <c r="K11" s="14" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="n"/>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="15" t="n"/>
-      <c r="H12" s="13" t="n"/>
-      <c r="I12" s="13" t="n"/>
-      <c r="J12" s="13" t="n"/>
-      <c r="K12" s="13" t="n"/>
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="14" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="14" t="n"/>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="16" t="n"/>
+      <c r="H12" s="14" t="n"/>
+      <c r="I12" s="14" t="n"/>
+      <c r="J12" s="14" t="n"/>
+      <c r="K12" s="14" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="n"/>
-      <c r="B13" s="13" t="n"/>
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="13" t="n"/>
-      <c r="E13" s="13" t="n"/>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="15" t="n"/>
-      <c r="H13" s="13" t="n"/>
-      <c r="I13" s="13" t="n"/>
-      <c r="J13" s="13" t="n"/>
-      <c r="K13" s="13" t="n"/>
+      <c r="A13" s="13" t="n"/>
+      <c r="B13" s="14" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="14" t="n"/>
+      <c r="F13" s="15" t="n"/>
+      <c r="G13" s="16" t="n"/>
+      <c r="H13" s="14" t="n"/>
+      <c r="I13" s="14" t="n"/>
+      <c r="J13" s="14" t="n"/>
+      <c r="K13" s="14" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="n"/>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="15" t="n"/>
-      <c r="H14" s="13" t="n"/>
-      <c r="I14" s="13" t="n"/>
-      <c r="J14" s="13" t="n"/>
-      <c r="K14" s="13" t="n"/>
+      <c r="A14" s="13" t="n"/>
+      <c r="B14" s="14" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="14" t="n"/>
+      <c r="E14" s="14" t="n"/>
+      <c r="F14" s="15" t="n"/>
+      <c r="G14" s="16" t="n"/>
+      <c r="H14" s="14" t="n"/>
+      <c r="I14" s="14" t="n"/>
+      <c r="J14" s="14" t="n"/>
+      <c r="K14" s="14" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="n"/>
-      <c r="B15" s="13" t="n"/>
-      <c r="C15" s="13" t="n"/>
-      <c r="D15" s="13" t="n"/>
-      <c r="E15" s="13" t="n"/>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="15" t="n"/>
-      <c r="H15" s="13" t="n"/>
-      <c r="I15" s="13" t="n"/>
-      <c r="J15" s="13" t="n"/>
-      <c r="K15" s="13" t="n"/>
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="14" t="n"/>
+      <c r="C15" s="14" t="n"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="15" t="n"/>
+      <c r="G15" s="16" t="n"/>
+      <c r="H15" s="14" t="n"/>
+      <c r="I15" s="14" t="n"/>
+      <c r="J15" s="14" t="n"/>
+      <c r="K15" s="14" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="n"/>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="15" t="n"/>
-      <c r="H16" s="13" t="n"/>
-      <c r="I16" s="13" t="n"/>
-      <c r="J16" s="13" t="n"/>
-      <c r="K16" s="13" t="n"/>
+      <c r="A16" s="13" t="n"/>
+      <c r="B16" s="14" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="14" t="n"/>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="16" t="n"/>
+      <c r="H16" s="14" t="n"/>
+      <c r="I16" s="14" t="n"/>
+      <c r="J16" s="14" t="n"/>
+      <c r="K16" s="14" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="n"/>
-      <c r="B17" s="13" t="n"/>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="15" t="n"/>
-      <c r="H17" s="13" t="n"/>
-      <c r="I17" s="13" t="n"/>
-      <c r="J17" s="13" t="n"/>
-      <c r="K17" s="13" t="n"/>
+      <c r="A17" s="13" t="n"/>
+      <c r="B17" s="14" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="14" t="n"/>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="16" t="n"/>
+      <c r="H17" s="14" t="n"/>
+      <c r="I17" s="14" t="n"/>
+      <c r="J17" s="14" t="n"/>
+      <c r="K17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="n"/>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="15" t="n"/>
-      <c r="H18" s="13" t="n"/>
-      <c r="I18" s="13" t="n"/>
-      <c r="J18" s="13" t="n"/>
-      <c r="K18" s="13" t="n"/>
+      <c r="A18" s="13" t="n"/>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="16" t="n"/>
+      <c r="H18" s="14" t="n"/>
+      <c r="I18" s="14" t="n"/>
+      <c r="J18" s="14" t="n"/>
+      <c r="K18" s="14" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="n"/>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="15" t="n"/>
-      <c r="H19" s="13" t="n"/>
-      <c r="I19" s="13" t="n"/>
-      <c r="J19" s="13" t="n"/>
-      <c r="K19" s="13" t="n"/>
+      <c r="A19" s="13" t="n"/>
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="14" t="n"/>
+      <c r="E19" s="14" t="n"/>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="16" t="n"/>
+      <c r="H19" s="14" t="n"/>
+      <c r="I19" s="14" t="n"/>
+      <c r="J19" s="14" t="n"/>
+      <c r="K19" s="14" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="n"/>
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="15" t="n"/>
-      <c r="H20" s="13" t="n"/>
-      <c r="I20" s="13" t="n"/>
-      <c r="J20" s="13" t="n"/>
-      <c r="K20" s="13" t="n"/>
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="14" t="n"/>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="16" t="n"/>
+      <c r="H20" s="14" t="n"/>
+      <c r="I20" s="14" t="n"/>
+      <c r="J20" s="14" t="n"/>
+      <c r="K20" s="14" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="n"/>
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="14" t="n"/>
-      <c r="G21" s="15" t="n"/>
-      <c r="H21" s="13" t="n"/>
-      <c r="I21" s="13" t="n"/>
-      <c r="J21" s="13" t="n"/>
-      <c r="K21" s="13" t="n"/>
+      <c r="A21" s="13" t="n"/>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="14" t="n"/>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="16" t="n"/>
+      <c r="H21" s="14" t="n"/>
+      <c r="I21" s="14" t="n"/>
+      <c r="J21" s="14" t="n"/>
+      <c r="K21" s="14" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="n"/>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="14" t="n"/>
-      <c r="G22" s="15" t="n"/>
-      <c r="H22" s="13" t="n"/>
-      <c r="I22" s="13" t="n"/>
-      <c r="J22" s="13" t="n"/>
-      <c r="K22" s="13" t="n"/>
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="16" t="n"/>
+      <c r="H22" s="14" t="n"/>
+      <c r="I22" s="14" t="n"/>
+      <c r="J22" s="14" t="n"/>
+      <c r="K22" s="14" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n"/>
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="14" t="n"/>
-      <c r="G23" s="15" t="n"/>
-      <c r="H23" s="13" t="n"/>
-      <c r="I23" s="13" t="n"/>
-      <c r="J23" s="13" t="n"/>
-      <c r="K23" s="13" t="n"/>
+      <c r="A23" s="13" t="n"/>
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="15" t="n"/>
+      <c r="G23" s="16" t="n"/>
+      <c r="H23" s="14" t="n"/>
+      <c r="I23" s="14" t="n"/>
+      <c r="J23" s="14" t="n"/>
+      <c r="K23" s="14" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="n"/>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="14" t="n"/>
-      <c r="G24" s="15" t="n"/>
-      <c r="H24" s="13" t="n"/>
-      <c r="I24" s="13" t="n"/>
-      <c r="J24" s="13" t="n"/>
-      <c r="K24" s="13" t="n"/>
+      <c r="A24" s="13" t="n"/>
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="16" t="n"/>
+      <c r="H24" s="14" t="n"/>
+      <c r="I24" s="14" t="n"/>
+      <c r="J24" s="14" t="n"/>
+      <c r="K24" s="14" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="n"/>
-      <c r="B25" s="13" t="n"/>
-      <c r="C25" s="13" t="n"/>
-      <c r="D25" s="13" t="n"/>
-      <c r="E25" s="13" t="n"/>
-      <c r="F25" s="14" t="n"/>
-      <c r="G25" s="15" t="n"/>
-      <c r="H25" s="13" t="n"/>
-      <c r="I25" s="13" t="n"/>
-      <c r="J25" s="13" t="n"/>
-      <c r="K25" s="13" t="n"/>
+      <c r="A25" s="13" t="n"/>
+      <c r="B25" s="14" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="14" t="n"/>
+      <c r="F25" s="15" t="n"/>
+      <c r="G25" s="16" t="n"/>
+      <c r="H25" s="14" t="n"/>
+      <c r="I25" s="14" t="n"/>
+      <c r="J25" s="14" t="n"/>
+      <c r="K25" s="14" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="n"/>
-      <c r="B26" s="13" t="n"/>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="14" t="n"/>
-      <c r="G26" s="15" t="n"/>
-      <c r="H26" s="13" t="n"/>
-      <c r="I26" s="13" t="n"/>
-      <c r="J26" s="13" t="n"/>
-      <c r="K26" s="13" t="n"/>
+      <c r="A26" s="13" t="n"/>
+      <c r="B26" s="14" t="n"/>
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="14" t="n"/>
+      <c r="E26" s="14" t="n"/>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="16" t="n"/>
+      <c r="H26" s="14" t="n"/>
+      <c r="I26" s="14" t="n"/>
+      <c r="J26" s="14" t="n"/>
+      <c r="K26" s="14" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="n"/>
-      <c r="B27" s="13" t="n"/>
-      <c r="C27" s="13" t="n"/>
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="14" t="n"/>
-      <c r="G27" s="15" t="n"/>
-      <c r="H27" s="13" t="n"/>
-      <c r="I27" s="13" t="n"/>
-      <c r="J27" s="13" t="n"/>
-      <c r="K27" s="13" t="n"/>
+      <c r="A27" s="13" t="n"/>
+      <c r="B27" s="14" t="n"/>
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="14" t="n"/>
+      <c r="E27" s="14" t="n"/>
+      <c r="F27" s="15" t="n"/>
+      <c r="G27" s="16" t="n"/>
+      <c r="H27" s="14" t="n"/>
+      <c r="I27" s="14" t="n"/>
+      <c r="J27" s="14" t="n"/>
+      <c r="K27" s="14" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="n"/>
-      <c r="B28" s="13" t="n"/>
-      <c r="C28" s="13" t="n"/>
-      <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="14" t="n"/>
-      <c r="G28" s="15" t="n"/>
-      <c r="H28" s="13" t="n"/>
-      <c r="I28" s="13" t="n"/>
-      <c r="J28" s="13" t="n"/>
-      <c r="K28" s="13" t="n"/>
+      <c r="A28" s="13" t="n"/>
+      <c r="B28" s="14" t="n"/>
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="14" t="n"/>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="16" t="n"/>
+      <c r="H28" s="14" t="n"/>
+      <c r="I28" s="14" t="n"/>
+      <c r="J28" s="14" t="n"/>
+      <c r="K28" s="14" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="n"/>
-      <c r="B29" s="13" t="n"/>
-      <c r="C29" s="13" t="n"/>
-      <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="14" t="n"/>
-      <c r="G29" s="15" t="n"/>
-      <c r="H29" s="13" t="n"/>
-      <c r="I29" s="13" t="n"/>
-      <c r="J29" s="13" t="n"/>
-      <c r="K29" s="13" t="n"/>
+      <c r="A29" s="13" t="n"/>
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="14" t="n"/>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="16" t="n"/>
+      <c r="H29" s="14" t="n"/>
+      <c r="I29" s="14" t="n"/>
+      <c r="J29" s="14" t="n"/>
+      <c r="K29" s="14" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="n"/>
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="14" t="n"/>
-      <c r="G30" s="15" t="n"/>
-      <c r="H30" s="13" t="n"/>
-      <c r="I30" s="13" t="n"/>
-      <c r="J30" s="13" t="n"/>
-      <c r="K30" s="13" t="n"/>
+      <c r="A30" s="13" t="n"/>
+      <c r="B30" s="14" t="n"/>
+      <c r="C30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="16" t="n"/>
+      <c r="H30" s="14" t="n"/>
+      <c r="I30" s="14" t="n"/>
+      <c r="J30" s="14" t="n"/>
+      <c r="K30" s="14" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="n"/>
-      <c r="B31" s="13" t="n"/>
-      <c r="C31" s="13" t="n"/>
-      <c r="D31" s="13" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="14" t="n"/>
-      <c r="G31" s="15" t="n"/>
-      <c r="H31" s="13" t="n"/>
-      <c r="I31" s="13" t="n"/>
-      <c r="J31" s="13" t="n"/>
-      <c r="K31" s="13" t="n"/>
+      <c r="A31" s="13" t="n"/>
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="16" t="n"/>
+      <c r="H31" s="14" t="n"/>
+      <c r="I31" s="14" t="n"/>
+      <c r="J31" s="14" t="n"/>
+      <c r="K31" s="14" t="n"/>
     </row>
     <row r="33">
-      <c r="D33" s="11" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>평균</t>
         </is>
       </c>
-      <c r="E33" s="16">
+      <c r="E33" s="17">
         <f>IF(COUNT(E2:E31)=0,"",AVERAGE(E2:E31))</f>
         <v/>
       </c>
-      <c r="F33" s="17">
+      <c r="F33" s="18">
         <f>IF(COUNT(F2:F31)=0,"",AVERAGE(F2:F31))</f>
         <v/>
       </c>
-      <c r="G33" s="18">
+      <c r="G33" s="19">
         <f>IF(COUNT(G2:G31)=0,"",AVERAGE(G2:G31))</f>
         <v/>
       </c>
-      <c r="H33" s="16">
+      <c r="H33" s="17">
         <f>IF(COUNT(H2:H31)=0,"",AVERAGE(H2:H31))</f>
         <v/>
       </c>
-      <c r="I33" s="16">
+      <c r="I33" s="17">
         <f>IF(COUNT(I2:I31)=0,"",AVERAGE(I2:I31))</f>
         <v/>
       </c>
-      <c r="J33" s="16">
+      <c r="J33" s="17">
         <f>IF(COUNT(J2:J31)=0,"",AVERAGE(J2:J31))</f>
         <v/>
       </c>
